--- a/01_INPUTS/objetivo 11T.xlsx
+++ b/01_INPUTS/objetivo 11T.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9C5265-1953-41BF-B78F-F13A9D24ED49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E88FA87-5DB1-4E3B-909E-9DD0A360DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2756557E-6E43-4FBF-8971-227ACF024C24}"/>
   </bookViews>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -151,6 +151,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -467,14 +470,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF24196A-8A5F-4013-B546-76F0D722BA4F}">
-  <dimension ref="B2:C13"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -482,93 +485,104 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="3">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="4">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="3">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="4">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="3">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="4">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="4">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="4">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="5">
-        <v>304</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
